--- a/artfynd/A 28212-2024 artfynd.xlsx
+++ b/artfynd/A 28212-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119088071</v>
+        <v>119088090</v>
       </c>
       <c r="B2" t="n">
-        <v>91822</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>535106</v>
+        <v>535155</v>
       </c>
       <c r="R2" t="n">
-        <v>6346097</v>
+        <v>6346146</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,59 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119088087</v>
+        <v>119088075</v>
       </c>
       <c r="B3" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Tönshult, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>535152</v>
+        <v>535054</v>
       </c>
       <c r="R3" t="n">
-        <v>6346161</v>
+        <v>6346166</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,59 +869,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119088082</v>
+        <v>119088071</v>
       </c>
       <c r="B4" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tönshult, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>535124</v>
+        <v>535106</v>
       </c>
       <c r="R4" t="n">
-        <v>6346139</v>
+        <v>6346097</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119088090</v>
+        <v>119088073</v>
       </c>
       <c r="B5" t="n">
-        <v>74622</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>306</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>535155</v>
+        <v>535038</v>
       </c>
       <c r="R5" t="n">
-        <v>6346146</v>
+        <v>6345959</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,59 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119088076</v>
+        <v>119088077</v>
       </c>
       <c r="B6" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tönshult, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>535100</v>
+        <v>535116</v>
       </c>
       <c r="R6" t="n">
-        <v>6346118</v>
+        <v>6346129</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,59 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119088078</v>
+        <v>119088083</v>
       </c>
       <c r="B7" t="n">
-        <v>100150</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tönshult, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>535169</v>
+        <v>535127</v>
       </c>
       <c r="R7" t="n">
-        <v>6346127</v>
+        <v>6346141</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119088088</v>
+        <v>119088074</v>
       </c>
       <c r="B8" t="n">
-        <v>5167</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1339,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>5420</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1363,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>535162</v>
+        <v>535015</v>
       </c>
       <c r="R8" t="n">
-        <v>6346165</v>
+        <v>6346076</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119088072</v>
+        <v>119088081</v>
       </c>
       <c r="B9" t="n">
-        <v>104984</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1441,43 +1365,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>6439</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tönshult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>535056</v>
+        <v>535121</v>
       </c>
       <c r="R9" t="n">
-        <v>6346042</v>
+        <v>6346135</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1536,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119088073</v>
+        <v>119243049</v>
       </c>
       <c r="B10" t="n">
-        <v>91822</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1552,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1576,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>535038</v>
+        <v>535096</v>
       </c>
       <c r="R10" t="n">
-        <v>6345959</v>
+        <v>6346025</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1606,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119088077</v>
+        <v>119088088</v>
       </c>
       <c r="B11" t="n">
-        <v>91822</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>535116</v>
+        <v>535162</v>
       </c>
       <c r="R11" t="n">
-        <v>6346129</v>
+        <v>6346165</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,15 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119088081</v>
+        <v>119088063</v>
       </c>
       <c r="B12" t="n">
-        <v>74620</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,34 +1656,38 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6439</v>
+        <v>208249</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Tönshult, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>535121</v>
+        <v>535133</v>
       </c>
       <c r="R12" t="n">
-        <v>6346135</v>
+        <v>6346142</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1842,15 +1746,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119088079</v>
+        <v>119088076</v>
       </c>
       <c r="B13" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1877,7 +1776,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1891,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>535173</v>
+        <v>535100</v>
       </c>
       <c r="R13" t="n">
-        <v>6346134</v>
+        <v>6346118</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,50 +1852,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119088083</v>
+        <v>119088079</v>
       </c>
       <c r="B14" t="n">
-        <v>91822</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Tönshult, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>535127</v>
+        <v>535173</v>
       </c>
       <c r="R14" t="n">
-        <v>6346141</v>
+        <v>6346134</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2055,42 +1958,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119088063</v>
+        <v>119088080</v>
       </c>
       <c r="B15" t="n">
-        <v>58164</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2099,10 +2002,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>535133</v>
+        <v>535128</v>
       </c>
       <c r="R15" t="n">
-        <v>6346142</v>
+        <v>6346149</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2161,15 +2064,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119088080</v>
+        <v>119088082</v>
       </c>
       <c r="B16" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2196,7 +2094,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2210,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>535128</v>
+        <v>535124</v>
       </c>
       <c r="R16" t="n">
-        <v>6346149</v>
+        <v>6346139</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2272,15 +2170,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119088085</v>
+        <v>119088084</v>
       </c>
       <c r="B17" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,7 +2200,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2321,10 +2214,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>535139</v>
+        <v>535130</v>
       </c>
       <c r="R17" t="n">
-        <v>6346196</v>
+        <v>6346201</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2383,15 +2276,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119088086</v>
+        <v>119088085</v>
       </c>
       <c r="B18" t="n">
-        <v>97889</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2418,7 +2306,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2432,10 +2320,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>535154</v>
+        <v>535139</v>
       </c>
       <c r="R18" t="n">
-        <v>6346152</v>
+        <v>6346196</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2494,50 +2382,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119243049</v>
+        <v>119088086</v>
       </c>
       <c r="B19" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tönshult, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>535096</v>
+        <v>535154</v>
       </c>
       <c r="R19" t="n">
-        <v>6346025</v>
+        <v>6346152</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2564,12 +2456,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2593,6 +2485,324 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>119088087</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Tönshult, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>535152</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6346161</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>119088072</v>
+      </c>
+      <c r="B21" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Tönshult, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>535056</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6346042</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>119088078</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Tönshult, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>535169</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6346127</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-08-12</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Patrik Celander</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 28212-2024 artfynd.xlsx
+++ b/artfynd/A 28212-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088090</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088075</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088071</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088073</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088077</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088083</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088074</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088081</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119243049</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088088</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1743,6 +1798,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088063</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1849,6 +1909,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088076</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1955,6 +2020,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088079</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2061,6 +2131,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088080</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2167,6 +2242,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088082</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2273,6 +2353,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088084</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2379,6 +2464,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088085</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2485,6 +2575,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088086</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2591,6 +2686,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088087</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2697,6 +2797,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088072</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2803,8 +2908,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119088078</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>